--- a/marketing_forms/015_mobile_app_launch_lead_generation_form--marketing_forms.xlsx
+++ b/marketing_forms/015_mobile_app_launch_lead_generation_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Word of mouth'}</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'online_advertisement'}</t>
+          <t>online_advertisement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Online advertisement'}</t>
+          <t>Online advertisement</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'message_in_app'}</t>
+          <t>message_in_app</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Message in app'}</t>
+          <t>Message in app</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'message_in_app'}</t>
+          <t>message_in_app</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Message in app'}</t>
+          <t>Message in app</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'message_in_app'}</t>
+          <t>message_in_app</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Message in app'}</t>
+          <t>Message in app</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'google_play'}</t>
+          <t>google_play</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Google play'}</t>
+          <t>Google play</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'apple_app_store'}</t>
+          <t>apple_app_store</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Apple app store'}</t>
+          <t>Apple app store</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'referral'}</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Referral'}</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'message_in_app'}</t>
+          <t>message_in_app</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Message in app'}</t>
+          <t>Message in app</t>
         </is>
       </c>
     </row>
